--- a/clino_scattering_planes_accessible.xlsx
+++ b/clino_scattering_planes_accessible.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,14 +510,14 @@
       <c r="I2" t="n">
         <v>15.24705525690479</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-hk0</t>
+          <t>-h-k0</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -533,29 +533,29 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>16.36557946754619</v>
+        <v>16.36546963123766</v>
       </c>
       <c r="I3" t="n">
-        <v>15.24571639765113</v>
-      </c>
-      <c r="J3" t="n">
+        <v>15.24693060735993</v>
+      </c>
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hkk</t>
+          <t>-hk0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -570,22 +570,22 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-20.38790312912558</v>
+        <v>16.36557946754619</v>
       </c>
       <c r="I4" t="n">
-        <v>14.75155044961241</v>
-      </c>
-      <c r="J4" t="n">
+        <v>15.24571639765113</v>
+      </c>
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>-hkk</t>
+          <t>-hk-h</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -595,7 +595,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -604,26 +604,26 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-20.38798492004405</v>
+        <v>34.49334922742212</v>
       </c>
       <c r="I5" t="n">
-        <v>14.75057443453965</v>
-      </c>
-      <c r="J5" t="n">
+        <v>310.2477336916563</v>
+      </c>
+      <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hk-h</t>
+          <t>-h-k-h</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -635,25 +635,25 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>39.89501358610413</v>
+        <v>34.49321932543143</v>
       </c>
       <c r="I6" t="n">
-        <v>84.38029043267113</v>
-      </c>
-      <c r="J6" t="n">
+        <v>310.2470893573069</v>
+      </c>
+      <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hk-k</t>
+          <t>hkk</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -672,49 +672,185 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>53.11834447701406</v>
+        <v>-20.38790312912558</v>
       </c>
       <c r="I7" t="n">
-        <v>15.03092225791461</v>
-      </c>
-      <c r="J7" t="n">
+        <v>14.75155044961241</v>
+      </c>
+      <c r="J7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>-hkk</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-20.38798492004405</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14.75057443453965</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>-h-k-k</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20.38793714860336</v>
+      </c>
+      <c r="I9" t="n">
+        <v>194.7511091117205</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>hk-h</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>39.89501358610413</v>
+      </c>
+      <c r="I10" t="n">
+        <v>84.38029043267113</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>hk-k</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>53.11834447701406</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15.03092225791461</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>-hk-k</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="B12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H12" t="n">
         <v>53.11831356662042</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I12" t="n">
         <v>15.03048069096935</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J12" t="b">
         <v>1</v>
       </c>
     </row>
